--- a/chapters/01/core/AIHE-A02/supp/AIHE-EX01/xlsx/AIHE-EX01_workbook.xlsx
+++ b/chapters/01/core/AIHE-A02/supp/AIHE-EX01/xlsx/AIHE-EX01_workbook.xlsx
@@ -61,48 +61,48 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="centre"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="centre" vertical="centre"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="centre"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="centre" vertical="centre"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="centre" vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="centre" vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="centre"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="centre" vertical="centre"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="centre"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="centre" vertical="centre"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="centre" vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="centre" vertical="centre" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
